--- a/artfynd/A 47483-2021 artfynd.xlsx
+++ b/artfynd/A 47483-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47483-2021 artfynd.xlsx
+++ b/artfynd/A 47483-2021 artfynd.xlsx
@@ -675,60 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100828719</v>
+        <v>100831653</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Bodås, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581489.5796638145</v>
+        <v>581336</v>
       </c>
       <c r="R2" t="n">
-        <v>6699064.471367616</v>
+        <v>6699160</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,73 +781,67 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100831653</v>
+        <v>100828719</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodås, Hofors, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581336.0236766515</v>
+        <v>581490</v>
       </c>
       <c r="R3" t="n">
-        <v>6699159.339959295</v>
+        <v>6699064</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -883,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -923,12 +913,7 @@
         <v>100834350</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581327.4011068486</v>
+        <v>581327</v>
       </c>
       <c r="R4" t="n">
-        <v>6699058.361110862</v>
+        <v>6699058</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1045,15 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104198165</v>
+        <v>104198112</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1090,21 +1070,17 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Österhästbo, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581315.4196154693</v>
+        <v>581522</v>
       </c>
       <c r="R5" t="n">
-        <v>6699063.033012244</v>
+        <v>6699015</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1134,19 +1110,9 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,15 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104198141</v>
+        <v>104198131</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1230,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581503.3226400441</v>
+        <v>581506</v>
       </c>
       <c r="R6" t="n">
-        <v>6699047.488230503</v>
+        <v>6699040</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1263,19 +1224,14 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Även gamla blomstänglar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,15 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104198157</v>
+        <v>104198141</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1289,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1359,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581449.4825442357</v>
+        <v>581504</v>
       </c>
       <c r="R7" t="n">
-        <v>6699065.052899383</v>
+        <v>6699048</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1392,19 +1343,9 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,15 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104198112</v>
+        <v>104198149</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1477,17 +1413,21 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Österhästbo, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581521.8724765972</v>
+        <v>581490</v>
       </c>
       <c r="R8" t="n">
-        <v>6699014.803185078</v>
+        <v>6699051</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1517,19 +1457,9 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,15 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104198171</v>
+        <v>104198157</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1517,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1613,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581320.4100544871</v>
+        <v>581449</v>
       </c>
       <c r="R9" t="n">
-        <v>6699061.168683489</v>
+        <v>6699065</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1646,24 +1571,9 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fanns även gamla blomstänglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,15 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104198149</v>
+        <v>104198165</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1631,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1747,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581489.3734951572</v>
+        <v>581316</v>
       </c>
       <c r="R10" t="n">
-        <v>6699051.62131677</v>
+        <v>6699063</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1780,19 +1685,9 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,15 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104198131</v>
+        <v>104198171</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1876,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581505.4564591703</v>
+        <v>581321</v>
       </c>
       <c r="R11" t="n">
-        <v>6699040.619386668</v>
+        <v>6699061</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1909,24 +1799,14 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Även gamla blomstänglar</t>
+          <t>Fanns även gamla blomstänglar.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 47483-2021 artfynd.xlsx
+++ b/artfynd/A 47483-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100831653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100828719</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100834350</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198131</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198149</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198157</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1712,6 +1757,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198165</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,8 +1881,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>